--- a/Lec/NLP/Assessment/论文调研.xlsx
+++ b/Lec/NLP/Assessment/论文调研.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\cloud-repository\Lec\NLP\Assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\迅雷下载\大四上\自然语言处理\assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A1473E-5AD0-4D11-8B6A-912BCAD6D590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FEA9E0-47DC-42E8-8675-C0B2AD59A73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="199">
   <si>
     <t>引用</t>
   </si>
@@ -143,12 +154,631 @@
     <t>幻觉问题</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>IJCAI-19</t>
+  </si>
+  <si>
+    <t>Automated Essay Scoring: A Survey of the State of the Art</t>
+  </si>
+  <si>
+    <t>Zixuan Ke and Vincent Ng. Automated Essay Scoring: A Survey of the State of the Art. Proceedings of the Twenty-Eighth International Joint Conference on Artificial Intelligence (IJCAI-19), 2019.</t>
+  </si>
+  <si>
+    <t>本文综述了AES自诞生以来的主要研究进展，涵盖整体评分与维度评分任务、监督学习与神经网络方法、特征工程与迁移学习策略，并指出未来研究应关注反馈质量、数据标注与多任务学习等方向。</t>
+  </si>
+  <si>
+    <t>系统回顾了AES的研究任务（整体/维度评分）、方法（监督学习、神经网络、迁移学习）与特征类型（词汇、句法、语义、论证等），并对比了各类方法在多个数据集上的表现。</t>
+  </si>
+  <si>
+    <t>未明确对比大模型，但提及神经网络方法（如LSTM、CNN、Attention）在AES中的应用，并指出BERT等预训练模型在未来具有潜力。</t>
+  </si>
+  <si>
+    <t>未涉及提示工程。</t>
+  </si>
+  <si>
+    <t>未涉及幻觉问题。</t>
+  </si>
+  <si>
+    <t>文章链接：https://www.ijcai.org/proceedings/2019/6300.pdf</t>
+  </si>
+  <si>
+    <t>自动作文评分（Automated Essay Scoring, AES）是自然语言处理（NLP）在教育领域最具代表性的应用之一，已有超过50年的研究历史。AES的研究初衷是为了减轻人工评分负担，尤其是在大规模标准化考试（如SAT、GRE）中，这类考试每年产生数百万篇作文，人工评分成本极高。因此，大多数AES系统最初聚焦于整体评分（holistic scoring），即为整篇作文打一个总分。然而，这种评分方式在教育场景中存在明显局限：学生仅得到一个分数，却无法了解自己在哪些方面存在不足，更无从改进。因此，近年来研究逐渐转向多维度评分（dimension-specific scoring），如语法、连贯性、论证力度、组织结构、中心论点清晰度、说服力等，以便为学生提供更具指导性的反馈。本文旨在综述AES领域自1966年以来的研究演进，系统梳理整体与维度评分任务、监督与神经网络方法、特征工程与迁移学习策略，并指出未来研究应关注反馈细化、数据标注与多任务学习等方向。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AES的研究始于1966年Page提出的Project Essay Grader系统，标志着该领域的正式起步。早期研究主要依赖特征工程+传统机器学习模型（如线性回归、SVM、贝叶斯分类器等），并聚焦于整体评分任务。随着深度学习的发展，神经网络模型（如CNN、LSTM、Attention机制）被引入AES系统，显著提升了评分性能，尤其是在大规模数据集（如ASAP、TOEFL11）上表现优异。然而，这些模型大多仍局限于整体评分，难以满足教育场景中对细粒度反馈的需求。为此，研究者开始构建支持维度评分的数据集（如ICLE、AAE），并探索如何对作文的组织结构、中心论点清晰度、论证说服力、连贯性等维度进行建模与评分。此外，迁移学习也被引入以解决训练数据不足的问题，尤其是在跨题目（cross-prompt）评分场景中。尽管近年来神经网络方法取得了显著进展，但特征工程方法仍在小样本、跨语言、维度评分等任务中发挥重要作用。作者强调，神经方法与特征工程应互为补充，而非替代。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务定义与分类：
+将AES任务划分为整体评分与维度评分两大类；
+维度评分包括：语法、用词、结构、连贯性、中心论点清晰度、说服力等。
+方法体系梳理：
+监督学习方法：将评分任务建模为回归、分类或排序问题；
+神经网络方法：从早期的CNN+LSTM模型，到引入注意力机制、文档结构建模、连贯性建模等；
+迁移学习方法：如EasyAdapt、Correlated Bayesian Regression、两阶段无目标题目训练框架等。
+特征体系归纳：
+系统总结了10类特征：长度、词汇、词嵌入、词类、题目相关性、可读性、句法、论证结构、语义、篇章结构；
+强调特征工程在低资源、维度评分任务中的持续价值。
+数据集对比分析：
+对比了5个主流数据集：CLC-FCE、ASAP、TOEFL11、ICLE、AAE；
+从语言类型、评分任务、标注维度、样本规模等维度进行系统分析。
+实验性能对比：
+汇总了各系统在主流数据集上的性能（QWK、PCC、MAE）；
+指出整体评分性能较高，维度评分仍有较大提升空间。
+未来方向展望：
+提出三大研究方向：
+反馈细化：不仅给出维度分数，还需解释为何得分低；
+数据标注：推动多维度标注统一 corpus，支持多任务学习；
+模型增强：探索BERT等预训练模型在AES中的应用潜力。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>arXiv 2020</t>
+  </si>
+  <si>
+    <t>Language Models are Few-Shot Learners</t>
+  </si>
+  <si>
+    <t>Brown, T. B., Mann, B., Ryder, N., Subbiah, M., Kaplan, J., Dhariwal, P., ... &amp; Amodei, D. (2020). Language models are few-shot learners. arXiv preprint arXiv:2005.14165.</t>
+  </si>
+  <si>
+    <t>GPT-3（175B）与T5、BERT、RoBERTa等模型对比，在多个任务上无需微调即可达到或超越其微调后的性能。例如，在TriviaQA上，GPT-3 few-shot达71.2%，超越T5-11B微调结果；在SuperGLUE上，GPT-3 few-shot平均得分73.2，接近微调后的T5-11B。</t>
+  </si>
+  <si>
+    <t>提示工程是本文核心方法之一。通过设计自然语言提示（如“Translate this sentence into French:”）和示例格式，引导模型完成特定任务。作者系统探索了不同提示格式对few-shot性能的影响，并发现提示设计对模型表现有显著影响。</t>
+  </si>
+  <si>
+    <t>尽管预训练+微调范式在NLP任务中取得巨大成功，但它仍依赖大量任务特定数据，且泛化能力有限。人类却能在极少示例或自然语言指令下完成新任务。本文提出通过扩大语言模型规模，可显著提升其在无需微调的情况下的任务适应能力，从而更接近人类的学习方式。</t>
+  </si>
+  <si>
+    <t>当前主流方法是预训练+微调，虽然性能强大，但需要大量标注数据，且模型容易过拟合特定任务分布，泛化性差。此外，构建大规模监督数据成本高昂，限制了模型在新任务上的快速适应能力。相比之下，人类具备从极少量示例中快速学习的能力（即few-shot learning），这启发了研究者探索任务无关、仅依赖提示的学习方式。</t>
+  </si>
+  <si>
+    <t>本文训练了拥有1750亿参数的GPT-3，系统评估其在zero-shot、one-shot 和 few-shot三种设置下的任务表现，涵盖翻译、问答、推理、阅读理解等20多个任务。结果表明，GPT-3在多数任务上无需微调即可达到或接近SOTA水平，展示了强大的上下文学习能力。同时，作者也指出其在某些任务（如NLI、阅读理解）上仍存在明显短板。</t>
+  </si>
+  <si>
+    <t>采用大规模自回归语言模型GPT-3，通过无监督预训练在海量文本上学习通用语言表示。在推理阶段，模型通过**自然语言提示（prompt）**和少量示例（demonstrations）进行任务适应，无需任何梯度更新。作者系统评估了不同模型规模（从125M到175B参数）在多种任务上的few-shot能力，并分析了其scaling behavior。</t>
+  </si>
+  <si>
+    <t>文中未明确提及“幻觉”一词，但在生成任务中，GPT-3存在事实错误、非逻辑推理、重复内容等问题。例如，在新闻生成任务中，模型生成的内容虽流畅，但常包含虚假事实，人类难以辨别，表明其存在幻觉生成风险。</t>
+  </si>
+  <si>
+    <t>1. 构建并训练8个不同规模的GPT-3模型（125M至175B参数）；
+2. 收集并清洗大规模训练语料（Common Crawl、WebText、Books、Wikipedia等），去重、过滤低质量内容；
+3. 在3000亿token上进行自回归预训练；
+4. 设计三类评估设置：zero-shot（仅任务描述）、one-shot（1个示例）、few-shot（10~100个示例）；
+5. 在20+ NLP任务上评估模型性能，包括语言建模、翻译、问答、推理、阅读理解、SuperGLUE等；
+6. 分析模型在不同任务上的scaling趋势，并检测训练数据与测试集之间的污染问题；
+7. 进行人类评估实验，测试GPT-3生成新闻文章的可信度与可检测性。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>Can large language models provide useful feedback on research papers?</t>
+  </si>
+  <si>
+    <t>Weixin Liang, Yuhui Zhang, Hancheng Cao, et al. arXiv preprint arXiv:2310.01783, 2023.</t>
+  </si>
+  <si>
+    <t>科学反馈是严谨研究的基石，但随着科研产出的指数级增长和学科高度专业化，传统的同行评审机制面临严峻挑战。高质量评审意见日益稀缺，尤其是初级研究者或资源匮乏地区的研究者更难获得及时反馈。大语言模型（LLM）如GPT-4的突破，引发了人们对其是否能生成有用科学反馈的兴趣。然而，目前尚缺乏系统性的实证研究来评估LLM生成反馈的实用性。为此，本文首次开展大规模实证研究，构建了一个基于GPT-4的自动化反馈生成系统，并通过回顾性与前瞻性分析评估其反馈质量与人类评审意见的一致性和实用性。</t>
+  </si>
+  <si>
+    <t>传统同行评审机制存在以下问题：1）评审成本高，估计每年耗费超过1亿小时和25亿美元；2）投稿量激增，ICLR会议投稿从2018年的960篇增至2023年的近5000篇；3）高质量评审资源分布不均，边缘群体更难获得有效反馈；4）评审延迟、偏见和疲劳问题严重。LLM在自然语言理解和生成方面表现优异，已被尝试用于论文筛选、错误识别等任务，但其在科学反馈中的可靠性和适用性尚未被系统验证。因此，本文提出构建一个基于GPT-4的科学反馈生成系统，并通过与人类评审意见的对比和用户研究，全面评估其效果。</t>
+  </si>
+  <si>
+    <t>本文系统评估了GPT-4生成科学反馈的能力。通过回顾性分析，比较了GPT-4与Nature系列期刊（3096篇）和ICLR会议（1709篇）中人类评审意见的重叠度，发现GPT-4与人类评审的意见重叠度（30.85%和39.23%）接近于两位人类评审之间的重叠度（28.58%和35.25%）。在前瞻性用户研究中，308位来自110所美国高校的研究者对其论文的GPT-4反馈进行评价，57.4%认为其有帮助，82.4%认为其优于部分人类评审。尽管GPT-4反馈存在一定局限性（如偏重实验建议、缺乏深入方法批判），但整体表明LLM反馈可作为人类评审的有益补充，尤其适用于初稿阶段或资源匮乏的研究者。</t>
+  </si>
+  <si>
+    <t>本文提出一个自动化的科学反馈生成系统，基于GPT-4对论文PDF进行解析并生成结构化反馈。系统包括两个阶段：1）PDF解析与提示构建；2）GPT-4生成反馈。反馈内容包括：1）重要性与新颖性；2）接受理由；3）拒稿理由；4）改进建议。系统采用零样本提示（zero-shot prompting），未进行微调或领域适配。为评估反馈质量，设计了回顾性与前瞻性两种评估方式：前者通过语义匹配比较GPT-4与人类评审意见的重叠度；后者通过用户调查收集研究者对反馈的主观评价。</t>
+  </si>
+  <si>
+    <t>1. PDF解析与提示构建：使用ScienceBeam工具提取论文标题、摘要、图表说明和正文前6500个token，构建提示模板，要求GPT-4生成四段式反馈。2. 回顾性评估：构建语义匹配管道，先提取GPT-4与人类评审意见中的评论点，再进行语义匹配，计算重叠度（Hit Rate、Jaccard、Dice等指标），并控制评论数量以消除偏差。3. 用户研究：搭建Gradio网页平台，邀请研究者上传其论文并接收GPT-4反馈，填写问卷评价反馈的有用性、具体性、与人类评审的对比等。4. 数据分析：统计反馈重叠度、用户满意度、反馈主题分布（如实验建议、创新性、伦理问题等），并进行分层分析（如不同期刊、接受/拒稿论文、评论顺序等）。</t>
+  </si>
+  <si>
+    <t>未与其他大模型（如Claude、Gemini）对比，仅使用GPT-4作为代表。研究指出未来可尝试其他模型或微调策略以提升反馈质量。</t>
+  </si>
+  <si>
+    <t>使用了精心设计的提示模板，要求GPT-4生成结构化评审意见，包括四部分内容，并限制生成风格为“高质量、建设性、具体”。提示模板对生成质量起到关键作用，但未涉及提示工程的系统性优化或对比实验。</t>
+  </si>
+  <si>
+    <t>文中未明确提及幻觉问题，但指出GPT-4反馈存在“泛化”或“模板化”倾向，如频繁建议“增加实验数据集”，可能与其训练数据中的偏见或生成模式有关。通过“打乱实验”验证其反馈具有论文特异性，间接回应了幻觉问题。</t>
+  </si>
+  <si>
+    <t>论文链接：https://arxiv.org/abs/2005.14165代码链接：https://github.com/Weixin-Liang/LLM-scientific-feedback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>论文链接：https://arxiv.org/abs/2310.01783 代码链接：https://github.com/Weixin-Liang/LLM-scientific-feedback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human-AI Collaborative Essay Scoring: A Dual-Process Framework with LLMs</t>
+  </si>
+  <si>
+    <t>Changrong Xiao, Wenxing Ma, Qingping Song, et al. arXiv preprint arXiv:2401.06431, 2024.</t>
+  </si>
+  <si>
+    <t>写作训练在第二语言学习中至关重要，但教师资源紧张导致反馈延迟，影响学生进步。自动化作文评分（AES）系统可提供即时反馈，缓解教师压力。然而，传统AES模型在多样化写作情境和模糊评分标准下表现不佳，且缺乏可解释性。为此，本文提出基于双过程理论的LLM-AES系统，旨在实现高精度评分、自然语言解释，并支持人机协同评分，提升教育公平与效率。</t>
+  </si>
+  <si>
+    <t>传统AES方法包括基于特征工程或深度学习的模型，如BERT、CNN、LSTM等，虽在评分准确率上有优势，但缺乏解释性，难以支持教师理解与干预。近期研究尝试引入LLM（如GPT-4、LLaMA3）进行评分，但零样本和少样本设置下性能仍不及SOTA模型。此外，教师普遍担心模型误判，需人工复核。为此，本文提出结合LLM评分与人工协同的新范式，借鉴心理学中的“快思维”与“慢思维”理论，构建可解释、可协同的AES系统。</t>
+  </si>
+  <si>
+    <t>本文提出一个基于双过程理论的开源LLM-AES系统，结合“快模块”（轻量分类器）与“慢模块”（微调LLaMA3），实现高效评分与高质量解释。实验表明，该系统在ASAP和CSEE数据集上评分性能接近SOTA，且解释质量与GPT-4相当。在人机协同评分实验中， novice评分者借助系统反馈可达到专家水平，专家评分者在效率和一致性上也有提升。系统通过置信度机制引导人工干预，实现高效协同。</t>
+  </si>
+  <si>
+    <t>提出“快-慢双模块”架构：快模块基于LLaMA3嵌入训练轻量分类器，快速输出分数与置信度；慢模块为微调后的LLaMA3，生成详细解释与评分。当置信度低于阈值（0.2）时，触发慢模块进行深度推理或人工介入。系统支持零样本、少样本、微调等多种设置，并结合Chain-of-Thought提示策略提升推理能力。</t>
+  </si>
+  <si>
+    <t>1. 数据准备：使用ASAP（12,978篇）与自建CSEE（13,372篇）数据集，后者由29所中国高中提供，按高考标准评分，涵盖内容、语言、结构三维度。2. 模型设计：快模块使用LLaMA3嵌入+全连接层，输出分数与置信度；慢模块为微调LLaMA3，生成解释与评分。3. 微调策略：使用GPT-4生成解释数据，构建指令微调数据集，训练LLaMA3与GPT-3.5。4. 提示设计：采用CoT策略，引导模型逐步分析作文内容、语言、结构并输出评分与解释。5. 人机协同实验：招募10名新手与5名专家评分者，先独立评分，后参考系统反馈进行修正，评估其评分一致性、效率与主观满意度。</t>
+  </si>
+  <si>
+    <t>对比了GPT-3.5、GPT-4、LLaMA3在零样本、少样本、微调设置下的评分性能。结果显示，GPT-4在零样本下表现较差，微调后LLaMA3与GPT-3.5性能接近，且LLaMA3具备开源、可控、成本低等优势。</t>
+  </si>
+  <si>
+    <t>使用了多种提示策略：零样本、少样本、带评分标准、Chain-of-Thought（CoT）等。实验表明，CoT与评分标准提示可显著提升模型理解能力与评分一致性。</t>
+  </si>
+  <si>
+    <t>文中未明确提及“幻觉”问题，但通过引入置信度机制与慢模块推理，间接缓解模型在低置信场景下可能产生的错误输出。此外，系统鼓励人工复核低置信评分，降低误判风险。</t>
+  </si>
+  <si>
+    <t>论文链接：https://arxiv.org/abs/2401.06431 代码链接：https://github.com/Xiaochr/LLM-AES</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMNLP 2004</t>
+  </si>
+  <si>
+    <t>TextRank: Bringing Order into Texts</t>
+  </si>
+  <si>
+    <t>Rada Mihalcea, Paul Tarau. TextRank: Bringing Order into Texts. EMNLP 2004.</t>
+  </si>
+  <si>
+    <t>本文提出一种基于图的排序模型 TextRank，用于自然语言文本中的无监督关键词提取和句子提取任务。该方法借鉴了 PageRank 的思想，通过构建词汇或句子之间的图结构，递归计算每个节点的重要性得分，从而识别文本中最具代表性的词语或句子。该方法无需训练数据，具有较强的通用性和可移植性。</t>
+  </si>
+  <si>
+    <t>传统的关键词提取和摘要方法多依赖于词频统计或监督学习，存在对语料依赖强、泛化能力差等问题。图排序算法（如 PageRank）在网页排序中取得成功，因其能利用全局结构信息进行递归推理。本文尝试将类似的图排序思想引入自然语言处理领域，提出 TextRank 模型，在无监督条件下实现关键词与重要句子的提取。</t>
+  </si>
+  <si>
+    <t>本文提出 TextRank 模型，一种基于图的无监督排序方法，用于关键词提取和句子提取。该方法通过构建文本单元（如词语或句子）之间的图结构，利用图排序算法（类似 PageRank）递归计算每个单元的重要性得分，从而识别出最具代表性的关键词或句子。实验表明，TextRank 在关键词提取任务中 F1 值优于当时最好的监督学习方法，在句子提取任务中也能生成质量较高的摘要。</t>
+  </si>
+  <si>
+    <t>TextRank 将文本表示为图结构，节点为文本单元（词或句子），边为它们之间的关系（如共现或内容重叠）。通过迭代计算每个节点的得分，直到收敛，最终按得分排序提取关键词或句子。该方法完全无监督，不依赖训练数据，适用于多种语言和领域。</t>
+  </si>
+  <si>
+    <t>1. 关键词提取：将词语作为节点，构建共现图（窗口大小为2~10），使用词性过滤（如仅保留名词和形容词），运行 TextRank 算法排序，提取 top 关键词，并合并相邻关键词为多词短语。2. 句子提取：将句子作为节点，计算句子间的内容重叠（使用归一化相似度），构建加权无向图，运行 TextRank 算法，提取得分最高的句子作为摘要。3. 排序算法：采用类似 PageRank 的迭代公式，考虑边的权重和方向，直至收敛。</t>
+  </si>
+  <si>
+    <t>未涉及大模型，TextRank 是基于图的传统方法，与现代的预训练语言模型（如 BERT、GPT）无直接对比。但其思想与后来基于图的神经网络模型（如 GNN、TextGCN）有一定关联。</t>
+  </si>
+  <si>
+    <t>无提示工程，TextRank 是无监督方法，不依赖提示或训练数据。</t>
+  </si>
+  <si>
+    <t>不涉及幻觉问题，TextRank 是基于图结构的确定性算法，不生成新文本，仅提取已有内容，不存在幻觉风险。</t>
+  </si>
+  <si>
+    <t>论文链接：https://aclanthology.org/W04-3252/
+项目页面：http://web.eecs.umich.edu/~mihalcea/papers/mihalcea.emnlp04.pdf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACL 2017</t>
+  </si>
+  <si>
+    <t>Get To The Point: Summarization with Pointer-Generator Networks</t>
+  </si>
+  <si>
+    <t>Abigail See, Peter J. Liu, Christopher D. Manning. Get To The Point: Summarization with Pointer-Generator Networks. ACL 2017.</t>
+  </si>
+  <si>
+    <t>本文指出，尽管神经序列到序列模型为生成式文本摘要提供了新路径，但其存在两个主要缺陷：容易生成错误的事实信息，以及倾向于重复输出内容。为此，作者提出了一种新的混合架构，通过引入指针机制和覆盖机制，提升摘要的准确性和多样性。</t>
+  </si>
+  <si>
+    <t>早期的摘要方法多为抽取式，即从原文中选取句子拼接而成，难以实现抽象概括。近年来，基于RNN的seq2seq模型被用于生成式摘要，但存在重复、幻觉、无法处理生僻词等问题。为此，研究者尝试引入注意力机制、复制机制（如CopyNet）等方式改进模型表现。本文在此基础上提出指针-生成器网络（Pointer-Generator），并结合覆盖机制（Coverage）以抑制重复。</t>
+  </si>
+  <si>
+    <t>本文提出一种混合指针-生成器网络架构，用于改进生成式文本摘要。该模型在标准seq2seq基础上引入两个关键机制：1）指针机制允许模型从原文中复制词语，提升对事实信息的准确复现能力；2）覆盖机制记录已关注过的内容，避免重复生成。该模型在CNN/Daily Mail数据集上显著超越当时的生成式摘要模型，ROUGE得分提升超过2分。</t>
+  </si>
+  <si>
+    <t>模型由三部分组成：1）标准seq2seq注意力模型作为baseline；2）指针-生成器网络，结合生成词与复制词的概率分布；3）覆盖机制，通过累加注意力分布构建覆盖向量，作为注意力机制输入并加入损失函数以抑制重复。模型使用双向LSTM编码器、单向LSTM解码器，训练采用Adagrad优化器，使用beam search解码。</t>
+  </si>
+  <si>
+    <t>1. 编码器：使用双向LSTM对输入文本进行编码，生成隐藏状态序列。2. 解码器：单向LSTM，结合上一时刻输出词嵌入与上下文向量生成当前状态。3. 注意力机制：计算每个时间步对源文本的注意力分布。4. 指针-生成器机制：计算生成概率 p_gen，决定从词汇表生成或从源文本复制。5. 覆盖机制：累加历史注意力分布，构建覆盖向量，作为注意力输入并加入覆盖损失。6. 训练与解码：使用负对数似然损失，加入覆盖损失项，使用beam search生成摘要。</t>
+  </si>
+  <si>
+    <t>未与GPT、BERT等大模型对比，但与当时SOTA的seq2seq模型（如Nallapati et al., 2016）相比，ROUGE得分提升显著。模型结构为传统RNN-based，未使用Transformer或预训练模型。</t>
+  </si>
+  <si>
+    <t>无提示工程，模型为端到端训练，不依赖提示模板或外部控制机制。</t>
+  </si>
+  <si>
+    <t>模型通过指针机制减少幻觉（如复制错误、生成不存在的词），但仍存在一定程度的抽象生成。覆盖机制有效抑制重复，但未完全消除幻觉问题。</t>
+  </si>
+  <si>
+    <t>论文链接：https://aclanthology.org/P17-1099/
+代码链接：https://github.com/abisee/pointer-generator</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>International Journal of Artificial Intelligence in Education (2017)</t>
+  </si>
+  <si>
+    <t>Automated Assessment of the Quality of Peer Reviews using Natural Language Processing Techniques</t>
+  </si>
+  <si>
+    <t>Lakshmi Ramachandran, Edward F. Gehringer, Ravi K. Yadav. Int J Artif Intell Educ (2017) 27:534–581.</t>
+  </si>
+  <si>
+    <t>本文旨在解决教育场景中同伴评审（peer review）质量参差不齐的问题。尽管同伴评审能促进学生写作与批判性思维，但学生往往缺乏评审经验，导致反馈质量不高。为此，作者提出一种自动化的“元评审”（metareview）系统，利用NLP技术对评审内容进行多维度质量评估，并即时反馈给评审者，帮助其改进评审质量。</t>
+  </si>
+  <si>
+    <t>传统评审质量评估依赖人工元评审，存在效率低、主观性强、难以规模化等问题。已有研究多聚焦于评审内容分类或情感分析，缺乏对评审质量的多维度系统性评估。本文提出一种基于图结构表示与语义匹配的自动化评估框架，涵盖内容类型、相关性、覆盖率、语气、文本量与抄袭检测六大指标，旨在提升评审质量与教学反馈效果。</t>
+  </si>
+  <si>
+    <t>本文提出一种基于NLP的自动化评审质量评估系统，涵盖六项核心指标：内容类型（总结/问题/建议）、相关性（与提交内容的语义匹配）、覆盖率（对提交主题句的覆盖）、语气（积极/消极/中性）、文本量（反馈长度）与抄袭检测。系统采用词序图（word-order graph）表示文本，结合语义相似度匹配与聚类技术，实现对评审内容的细粒度分析。实验表明，系统在内容分类、相关性识别与覆盖率评估等方面优于传统机器学习方法，且用户反馈积极。</t>
+  </si>
+  <si>
+    <t>系统采用词序图表示评审与提交文本，通过图匹配计算语义相似度，识别评审内容类型、相关性与覆盖率。具体包括：1）构建图结构表示文本句法与语义关系；2）使用WordNet进行多类型语义匹配（同义、上下位、整体部分等）；3）基于图的聚类提取提交文本主题句；4）计算评审与主题句的覆盖度；5）结合规则与词典识别语气与抄袭；6）输出可视化反馈供评审者查看。</t>
+  </si>
+  <si>
+    <t>1. 内容类型识别：使用图结构提取高频边模式，识别总结、问题、建议三类内容，F1值达0.67，优于SVM与LR。2. 相关性识别：通过词序图匹配评审与提交文本，支持短语、上下文、句法三层匹配，准确率达66%，优于依赖树基线与n-gram重叠方法。3. 覆盖率识别：使用凝聚式聚类提取提交主题句，计算评审与主题句的语义重叠，与人类评分的相关性达0.49，优于MEAD与Opinosis摘要系统。4. 语气识别：基于情感词典识别积极、消极、中性语气。5. 文本量：统计评审中独特词数。6. 抄袭检测：检测评审是否复制提交内容或他人评审。</t>
+  </si>
+  <si>
+    <t>未涉及大模型，系统基于传统NLP方法（图匹配、聚类、规则、WordNet），未使用BERT、GPT等预训练模型。</t>
+  </si>
+  <si>
+    <t>无提示工程，系统为全自动分析流程，不依赖提示或交互式输入。</t>
+  </si>
+  <si>
+    <t>未明确讨论幻觉问题，但系统通过图匹配与语义相似度计算，避免生成虚假内容，专注于对现有文本的分析与评估。</t>
+  </si>
+  <si>
+    <t>论文链接：https://link.springer.com/article/10.1007/s40593-016-0114-8</t>
+  </si>
+  <si>
+    <t>NDSS 2019</t>
+  </si>
+  <si>
+    <t>NAUTILUS: Fishing for Deep Bugs with Grammars</t>
+  </si>
+  <si>
+    <t>Cornelius Aschermann, Patrick Jauernig, Tommaso Frassetto, et al. NDSS 2019.</t>
+  </si>
+  <si>
+    <t>本文指出，传统模糊测试（fuzzing）在测试需要高度结构化输入的程序（如解释器）时，难以通过语法和语义检查，导致无法触达深层代码逻辑。为此，作者提出 NAUTILUS，一种结合上下文无关文法（CFG）与代码覆盖率反馈的混合模糊测试方法，可生成语法正确且语义有效的输入，从而高效发现深层漏洞。</t>
+  </si>
+  <si>
+    <t>模糊测试是发现软件漏洞的有效手段，但在面对解释器等需要复杂输入格式的程序时，传统基于变异的模糊器（如AFL）难以生成有效输入，常被语法检查拦截。文法驱动的模糊器虽能生成语法正确的输入，但缺乏反馈机制，无法指导输入生成方向。NAUTILUS 首次将文法生成与覆盖率反馈结合，实现无需初始语料库的高效深层模糊测试。</t>
+  </si>
+  <si>
+    <t>本文提出 NAUTILUS，一种基于文法与覆盖率反馈的模糊测试框架，专为需要结构化输入的程序设计。系统从文法生成初始输入，利用覆盖率反馈指导变异与重组，生成语法与语义均有效的输入。实验表明，NAUTILUS 在 mruby、PHP、Lua 和 ChakraCore 中发现多个未知漏洞，覆盖率提升达28个百分点，显著优于 AFL 和传统文法模糊器。</t>
+  </si>
+  <si>
+    <t>NAUTILUS 采用“文法生成 + 反馈变异”的混合架构：1）使用 CFG 生成初始输入；2）通过覆盖率反馈识别“有趣”输入；3）在推导树上执行结构变异（如子树替换、递归扩展、拼接）；4）最小化输入以保持高效；5）支持自定义脚本扩展文法，处理非上下文无关结构（如 XML 标签匹配）。</t>
+  </si>
+  <si>
+    <t>1. 预处理：解析文法（支持 ANTLR 格式），预计算非终结符最小生成长度、子树数量等；2. 初始输入生成：使用 naive 或 uniform 策略生成 1000 个随机推导树；3. 执行与反馈：通过 forkserver 执行输入，记录基本块转换，识别新路径；4. 最小化：使用子树最小化与递归最小化，去除冗余结构；5. 变异：包括规则变异、随机递归、拼接、AFL 风格位翻转等；6. 调度器：按状态（init/det/detafl/random）分阶段处理输入，优先探索高潜力路径；7. 输出：保存崩溃输入与覆盖信息。</t>
+  </si>
+  <si>
+    <t>未涉及大模型，NAUTILUS 基于文法与符号执行，与 LLM 无关。其创新在于将文法生成与覆盖率反馈结合，而非依赖数据驱动模型。</t>
+  </si>
+  <si>
+    <t>无提示工程，系统为全自动模糊测试流程，不依赖提示或模板。</t>
+  </si>
+  <si>
+    <t>未涉及幻觉问题，NAUTILUS 生成的是结构化程序输入，非自然语言文本，不存在幻觉风险。其挑战在于如何生成语义有效的输入，而非生成虚假内容。</t>
+  </si>
+  <si>
+    <t>论文链接：https://www.ndss-symposium.org/ndss-paper/nautilus-fishing-for-deep-bugs-with-grammars/
+代码链接：https://github.com/RUB-SysSec/nautilus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NIPS 2017</t>
+  </si>
+  <si>
+    <t>Attention Is All You Need</t>
+  </si>
+  <si>
+    <t>Vaswani, A., Shazeer, N., Parmar, N., Uszkoreit, J., Jones, L., Gomez, A. N., ... &amp; Polosukhin, I. (2017). Attention is all you need. In Advances in neural information processing systems (pp. 5998-6008).</t>
+  </si>
+  <si>
+    <t>传统的序列建模方法（如RNN、LSTM）在处理序列时依赖于逐步计算，难以并行化，训练效率低。尽管已有注意力机制被引入以捕捉长距离依赖，但它们通常仍与RNN结构结合使用。本文提出了一种全新的思路：完全摒弃RNN和卷积结构，仅依赖注意力机制构建模型，从而实现更高的并行化能力和训练效率。</t>
+  </si>
+  <si>
+    <t>当前主流的序列建模方法（如RNN、LSTM、GRU）在机器翻译、语言建模等任务中表现优异，但由于其顺序计算的本质，难以充分利用现代硬件的并行能力。虽然已有研究尝试通过卷积网络（如ConvS2S、ByteNet）减少顺序计算，但它们在捕捉长距离依赖方面仍存在效率瓶颈。注意力机制已被广泛用于增强模型对序列中关键部分的关注，但大多数模型仍将其作为RNN的辅助工具。</t>
+  </si>
+  <si>
+    <t>本文提出Transformer模型，一种完全基于注意力机制的序列建模架构，摒弃了传统的RNN和卷积结构。该模型通过多头自注意力机制捕捉序列内部依赖关系，并引入位置编码以保留序列顺序信息。实验表明，Transformer在WMT 2014英德和英法翻译任务上取得了当时最好的性能，且训练时间显著缩短。</t>
+  </si>
+  <si>
+    <t>Transformer采用编码器-解码器结构，核心为多头自注意力机制和位置前馈网络。编码器和解码器均由多层堆叠而成，每层包含残差连接和层归一化。模型通过注意力机制实现序列中任意位置之间的直接建模，提升并行性和训练效率。</t>
+  </si>
+  <si>
+    <t>与RNN（LSTM/GRU）和CNN（ConvS2S、ByteNet）等主流模型相比，Transformer在训练速度、并行性和翻译质量上均表现更优，尤其在长距离依赖建模方面具有显著优势。</t>
+  </si>
+  <si>
+    <t>未涉及</t>
+  </si>
+  <si>
+    <t>1. 输入嵌入与位置编码：将输入词嵌入与正弦位置编码相加，保留词序信息。
+2. 多头自注意力机制：将查询、键、值向量映射到多个子空间，分别计算注意力后拼接，增强模型对不同语义子空间的关注能力。
+3. 前馈神经网络：每个位置独立通过两层线性变换+ReLU激活，进一步提取特征。
+4. 残差连接与层归一化：每子层输出与输入相加并归一化，稳定训练。
+5. 编码器-解码器注意力：解码器通过注意力机制访问编码器输出，实现跨序列信息融合。
+6. 掩码机制：解码器自注意力使用掩码，防止信息泄露，确保自回归性质。
+7. 输出层：通过线性变换和Softmax生成目标词概率分布。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSAI 2024</t>
+  </si>
+  <si>
+    <t>On Automated Essay Grading using Large Language Models</t>
+  </si>
+  <si>
+    <t>Liew, P. Y., &amp; Tan, I. K. T. (2024). On Automated Essay Grading using Large Language Models. In CSAI '24: Proceedings of the 2024 8th International Conference on Computer Science and Artificial Intelligence (pp. 204–211). ACM.</t>
+  </si>
+  <si>
+    <t>传统人工评分主观性强、耗时费力，存在评分不一致的问题。AES（自动评分）与AWE（自动写作反馈）系统应运而生，但传统方法依赖特征工程或深度学习模型，泛化能力有限。本文指出，随着大模型（如GPT-4、PaLM、LLaMA2）的发展，其在语言理解与生成上的能力为AEG任务提供了新的可能性。研究旨在探索LLM在AES与AWE中的潜力，并通过提示工程优化其表现。</t>
+  </si>
+  <si>
+    <t>AES起源于1966年的PEG系统，逐步发展为基于NLP、LSA、CNN、LSTM等技术的评分系统，并被应用于GRE、TOEFL等考试中。AWE则关注为学生提供个性化、具体、及时的写作反馈，传统系统如e-rater、Criterion等已广泛应用。随着LLM（如GPT、PaLM、LLaMA）崛起，其在文本理解与生成方面表现优异，提示工程成为引导模型行为的关键手段，为AEG任务带来新机遇。</t>
+  </si>
+  <si>
+    <t>本文系统评估了GPT-3.5、GPT-4、PaLM和LLaMA2在AES（评分）与AWE（反馈）任务中的表现，结合提示工程优化模型输出。实验显示，GPT-3.5在AES任务中达到0.618的QWK评分（与人类评分呈“substantial agreement”），在AWE任务中反馈质量平均得分达4.9/5，表现出与人类高度一致的评价能力。研究表明，LLM在无微调条件下已具备较强的AEG能力。</t>
+  </si>
+  <si>
+    <t>研究采用提示工程方法，评估多种LLM在AES与AWE任务中的表现。通过设计不同提示（如评分标准、写作类型、反馈风格等），引导模型生成评分或反馈。最终选择GPT-3.5作为性价比最高的模型，并进一步优化提示以提升其在评分一致性与反馈质量上的表现。</t>
+  </si>
+  <si>
+    <t>对比了GPT-3.5、GPT-4、PaLM和LLaMA2在AEG任务中的表现。结果显示，GPT-4评分略优于GPT-3.5，但成本更高；PaLM与LLaMA2表现较差。综合考虑性能与成本，GPT-3.5为最佳选择。</t>
+  </si>
+  <si>
+    <t>提示工程为核心方法，研究系统设计了多种提示（如评分标准、写作类型、反馈风格等），并通过实验验证其对模型输出的显著影响。最终提示在评分一致性与反馈质量上均取得最佳效果。</t>
+  </si>
+  <si>
+    <t>未明确提及幻觉问题，但指出模型可能存在偏见，且对创造性、批判性思维等难以量化，暗示幻觉或误判可能影响评分公正性。</t>
+  </si>
+  <si>
+    <t>1. 数据集选择：使用IELTS写作评分数据集，包含1400+篇已评分作文及评分理由。
+2. 模型选择：评估GPT-3.5、GPT-4、PaLM、LLaMA2在AES与AWE任务中的表现。
+3. 提示设计：为每个模型设计多个提示（如评分标准、写作类型、反馈风格等），覆盖评分与反馈任务。
+4. 评分评估：使用QWK（Quadratic Weighted Kappa）衡量模型评分与人类评分的一致性。
+5. 反馈评估：通过人工评分（1–5分）评估模型生成反馈的质量与一致性。
+6. 提示优化：在GPT-3.5上进一步微调提示，提升其在评分与反馈任务中的表现。
+7. 人工验证：邀请两位英语教师对模型评分与反馈进行人工评估，验证其可靠性与实用性。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LREC-COLING 2024</t>
+  </si>
+  <si>
+    <t>Is LLM a Reliable Reviewer? A Comprehensive Evaluation of LLM on Automatic Paper Reviewing Tasks</t>
+  </si>
+  <si>
+    <t>Zhou, R., Chen, L., &amp; Yu, K. (2024). Is LLM a Reliable Reviewer? A Comprehensive Evaluation of LLM on Automatic Paper Reviewing Tasks. In Proceedings of the 2024 Joint International Conference on Computational Linguistics, Language Resources and Evaluation (LREC-COLING 2024), pages 9340–9351.</t>
+  </si>
+  <si>
+    <t>随着学术论文数量激增，获取及时、专业的同行评审意见愈发困难。大语言模型（LLM）在阅读理解、知识整合和逻辑推理方面表现突出，因此引发研究者的广泛关注：LLM是否可以作为合格的自动评审者？本文系统评估了GPT-3.5与GPT-4在论文评审任务中的可靠性，发现其虽能提供有用建议，但仍存在显著缺陷，尚不足以完全胜任自动评审任务。</t>
+  </si>
+  <si>
+    <t>自动评审任务已有多年研究历史，早期方法主要基于分类模型预测论文接受与否，或生成评审文本。近年来，随着LLM的发展，研究者开始探索其在评审文本生成、元评审、编辑建议等任务中的应用。然而，现有研究多聚焦于生成质量或一致性，缺乏对模型“正确性”与“批判性”能力的深入评估。本文指出，当前LLM在评审任务中仍存在逻辑推理弱、缺乏专业知识、对长文本处理能力有限等问题。</t>
+  </si>
+  <si>
+    <t>本文系统评估了GPT-3.5与GPT-4在自动论文评审任务中的表现，涵盖评分预测与评审文本生成两大任务，并提出一个包含196道选择题的RR-MCQ数据集，用于评估模型对评审与修改建议的理解能力。实验表明，LLM在评分预测任务中表现尚可（给定评审文本时相关性达0.65），但在直接阅读论文后评分、生成有深度的评审意见、回答涉及逻辑与知识的选择题方面表现不佳。研究结论指出，LLM尚不具备成为可靠自动评审者的能力。</t>
+  </si>
+  <si>
+    <t>研究从三方面评估LLM的评审能力：（1）评分预测任务，基于评审文本或论文内容预测各项评分；（2）评审文本生成任务，生成ICLR风格的评审意见；（3）设计RR-MCQ数据集，评估模型对评审与修改建议的理解与推理能力。通过自动指标与人工评估相结合，全面分析模型的评审能力。</t>
+  </si>
+  <si>
+    <t>主要对比GPT-3.5与GPT-4。结果显示，GPT-4在评分预测、评审生成与RR-MCQ任务中均优于GPT-3.5，但仍存在显著缺陷，如在生成评审中偏好正面评价、缺乏批判性，在RR-MCQ中完全正确率仅约20%。</t>
+  </si>
+  <si>
+    <t>提示工程为关键方法，研究设计了多种提示风格（如zero-shot、few-shot、MCQ风格）以引导模型完成评分预测与评审生成任务，并发现MCQ风格提示对评分预测帮助有限，few-shot提示有助于生成更平衡的评审意见。</t>
+  </si>
+  <si>
+    <t>研究指出LLM在生成评审时存在“幻觉”问题，如生成内容空洞、缺乏技术细节、偏好正面评价、回避批判性意见，且在面对需逻辑推理与知识判断的问题时容易出错，表明其尚未具备可靠的评审能力。</t>
+  </si>
+  <si>
+    <t>1. 评分预测任务：使用PeerRead数据集中ICLR-2017子集，评估模型在“给定评审文本”或“给定论文内容”两种情况下的评分预测能力，采用zero-shot、few-shot和MCQ风格提示。
+2. 评审生成任务：使用ASAP数据集中ICLR-2020子集，生成带标签的评审文本，评估其覆盖率、相似性与信息丰富度。
+3. RR-MCQ数据集构建：从ICLR-2023评审-回复论坛中提取55条评审，设计196道选择题，涵盖评审内容、修改建议、逻辑推理等方面。
+4. 提示设计：为不同任务设计多种提示风格（如zero-shot、few-shot、MCQ风格），引导模型生成评分或评审文本。
+5. 评估指标：评分预测采用Pearson、Spearman、Kendall相关系数；评审生成采用ROUGE、BERTScore、BLANC及人工评分；RR-MCQ采用准确率、精确率、召回率与F1值。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2024.lrec-main.816/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scientific Reports (2025)</t>
+  </si>
+  <si>
+    <t>An LLM-based hybrid approach for enhanced automated essay scoring</t>
+  </si>
+  <si>
+    <t>传统AES方法多依赖浅层语言特征（如词频、句长等），忽视了文本结构和语义信息，导致评分结果与人工评分一致性有限。为此，本文提出一种融合浅层特征、篇章模式与GPT生成上下文嵌入的混合模型，以更全面地捕捉文本连贯性与复杂性，从而提升评分准确性和鲁棒性。</t>
+  </si>
+  <si>
+    <t>AES研究经历了从浅层特征（如E-rater）到神经网络嵌入（如BERT、GPT）再到篇章结构建模的发展过程。尽管深度学习方法在语义建模方面表现更好，但仍面临难以兼顾语言表层特征与深层语义的挑战。本文指出，将GPT生成的上下文嵌入与传统语言特征融合，有望弥补单一模型的不足。</t>
+  </si>
+  <si>
+    <t>本文提出一种融合浅层语言特征、篇章模式与GPT-3上下文嵌入的混合AES模型。该方法通过提取可读性、词汇多样性、语法、复杂度等指标，并结合GPT生成的句子级语义嵌入，训练随机森林分类器进行评分预测。实验表明，该模型在多个标准数据集上优于传统浅层方法、纯GPT模型及主流商业系统（如e-rater、IntelliMetric），QWK平均达0.83，显著提升评分一致性。</t>
+  </si>
+  <si>
+    <t>模型由三部分组成：1）浅层语言特征提取（可读性、词汇多样性、语法、复杂度等）；2）篇章模式建模（基于实体网格与语义相似度）；3）GPT-3上下文嵌入生成（句子级语义表示）。三者融合后输入随机森林分类器进行评分预测。</t>
+  </si>
+  <si>
+    <t>与纯GPT-3、DP+SF、SAGE、PEG、e-rater、IntelliMetric等系统对比，混合模型在QWK、EA、AA等指标上均表现更优，平均QWK达0.83，显著优于GPT-only（0.71）和商业系统（0.73–0.78）。</t>
+  </si>
+  <si>
+    <t>未涉及提示工程，模型直接使用GPT-3生成句子嵌入，未通过提示引导生成评分或反馈。</t>
+  </si>
+  <si>
+    <t>未明确提及幻觉问题，但指出GPT存在对训练集外词汇嵌入能力弱的问题，可能影响对自由文本的评分准确性。</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41598-025-87862-3</t>
+  </si>
+  <si>
+    <t>Atkinson, J., &amp; Palma, D. (2025). An LLM-based hybrid approach for enhanced automated essay scoring. Scientific Reports, 15, 14551. https://doi.org/10.1038/s41598-025-87862-3</t>
+  </si>
+  <si>
+    <t>1. 数据准备：使用Kaggle AES竞赛数据集，包括8个子集，涵盖议论文、叙述文、说明文等类型；
+2. 特征提取：提取浅层特征（如Gunning-Fog、FRE、GI、代词密度等）、篇章模式（实体转移概率、语义相似度）与GPT-3句子嵌入；
+3. 模型训练：使用10折交叉验证训练随机森林回归/分类器；
+4. 评估指标：采用QWK、EA、AA、Spearman相关系数评估模型性能；
+5. 对比实验：与DP+SF、GPT-only、SAGE、PEG、e-rater等系统对比，验证混合模型优势。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/1706.03762</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+https://dl.acm.org/doi/10.1145/3709026.3709030</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Research Methods in Applied Linguistics (2023)</t>
+  </si>
+  <si>
+    <t>Exploring the potential of using an AI language model for automated essay scoring</t>
+  </si>
+  <si>
+    <t>随着ChatGPT等大语言模型的普及，其在语言理解与生成方面展现出强大能力，引发了将其用于自动作文评分（AES）的研究兴趣。本文旨在评估GPT-3模型在AES任务中的可靠性与准确性，并探讨语言学特征对其评分性能的影响，为AI辅助写作评估提供实证支持。</t>
+  </si>
+  <si>
+    <t>AES研究始于20世纪60年代，早期方法依赖浅层特征（如句长、标点数），易被操控。90年代后，随着NLP发展，e-rater等系统引入语法、语义分析。近年来，深度学习（如CNN、BERT、GPT）被广泛应用于AES，显著提升了评分准确性。GPT虽以生成任务为主，但其提示学习能力使其在评分任务中具有潜力，尚未被系统研究。</t>
+  </si>
+  <si>
+    <t>本文使用GPT-3（text-davinci-003）对TOEFL11数据集中12,100篇非母语英语作文进行评分，并与人工评分对比。结果显示，GPT评分在三种等级（低、中、高）间具有显著区分度，QWK为0.682，表现出“substantial”一致性。进一步结合45种语言学特征（词汇、句法、衔接）后，评分准确性显著提升，QWK达0.605，表明GPT在AES中具有可行性与增强潜力。</t>
+  </si>
+  <si>
+    <t>研究采用提示学习方式，将IELTS写作评分标准作为提示输入GPT-3，对作文进行0–9分评分，并抽取1,210篇作文进行重测以评估一致性。随后，构建7个贝叶斯序数回归模型，比较GPT评分与语言学特征结合后的预测能力，采用LOOIC进行模型比较，QWK与伪R²作为评估指标。</t>
+  </si>
+  <si>
+    <t>未与其他大模型（如GPT-4、BERT、PaLM）直接对比，但指出GPT-3在zero-shot条件下已具备较强评分能力，且结合语言学特征后性能优于传统机器学习模型。</t>
+  </si>
+  <si>
+    <t>使用zero-shot提示工程，将IELTS评分标准嵌入提示中，未提供样例作文，以避免偏差。研究指出提示设计对评分结果有显著影响，但未进一步探索few-shot或链式提示等策略。</t>
+  </si>
+  <si>
+    <t>未明确提及幻觉问题，但指出GPT评分存在一定偏差（如评分集中于4–8分），且无法完全解释其评分依据，建议未来研究结合可解释AI（XAI）方法提升透明度。</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.rmal.2023.100050</t>
+  </si>
+  <si>
+    <t>Mizumoto, A., &amp; Eguchi, M. (2023). Exploring the potential of using an AI language model for automated essay scoring. Research Methods in Applied Linguistics, 2, 100050. https://doi.org/10.1016/j.rmal.2023.100050</t>
+  </si>
+  <si>
+    <t>1. 数据准备：使用TOEFL11数据集，包含12,100篇来自11种母语背景的英语作文，每篇已标注低、中、高三个等级；
+2. 提示设计：使用IELTS写作评分标准（0–9分）作为提示，不包含样例作文，采用zero-shot方式评分；
+3. 自动评分：调用OpenAI text-davinci-003 API对所有作文进行评分，并抽取1,210篇进行重测以评估一致性；
+4. 特征提取：使用TAALED、TAALES、TAASSC、TAACO等工具提取45种语言学特征，涵盖词汇多样性、复杂度、句法、衔接等；
+5. 模型构建：构建7个贝叶斯序数回归模型（GPT-only、GPT+各类特征、仅特征），使用LOOIC比较模型拟合优度；
+6. 评估指标：采用QWK、伪R²、EA、AA等指标评估评分一致性与预测准确性。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Research Integrity and Peer Review (2023)</t>
+  </si>
+  <si>
+    <t>Fighting reviewer fatigue or amplifying bias? Considerations and recommendations for use of ChatGPT and other large language models in scholarly peer review</t>
+  </si>
+  <si>
+    <t>随着ChatGPT等大语言模型（LLMs）的广泛应用，其在学术写作和同行评审中的潜力与风险引发关注。本文探讨了LLMs在同行评审中的潜在作用，指出其可能缓解评审疲劳、提升效率，但也可能加剧偏见、破坏评审的透明性与可重复性，呼吁制定使用规范与伦理指南。</t>
+  </si>
+  <si>
+    <t>同行评审是学术出版的核心环节，但面临评审疲劳、质量参差不齐、语言障碍等问题。LLMs如ChatGPT具备生成流畅文本、总结内容、提供反馈的能力，已被部分学者用于撰写评审意见或辅助编辑工作。然而，LLMs的训练数据不透明、输出不可重复、可能存在偏见，且对输入文本的处理方式不明，带来数据安全与伦理风险。</t>
+  </si>
+  <si>
+    <t>本文基于Tennant和Ross-Hellauer提出的五个同行评审核心主题（评审者角色、编辑角色、评审功能与质量、可重复性、社会与认识论功能），系统探讨LLMs在同行评审中的潜在影响。通过案例分析与ChatGPT交互实验，发现LLMs可提升评审效率、改善语言表达，但也存在偏见放大、数据泄露、评审质量不可控等风险。作者建议在使用LLMs时应披露使用方式、接受责任、加强培训，并呼吁制定明确的政策与伦理规范。</t>
+  </si>
+  <si>
+    <t>文章采用理论分析与案例实验相结合的方法，围绕五个核心主题展开讨论，并通过与ChatGPT的交互示例（如生成评审意见、评估方法描述、撰写讽刺性评审等）展示LLMs在实际评审场景中的表现与潜在问题。</t>
+  </si>
+  <si>
+    <t>主要以ChatGPT为例进行探讨，未与其他LLM（如GPT-4、Claude、PaLM等）进行系统对比，但指出不同模型可能在偏见、语言风格、可用性等方面存在差异。</t>
+  </si>
+  <si>
+    <t>强调提示工程对LLMs输出的影响，指出即使是微小的提示差异也可能导致截然不同的评审风格或结论，建议用户在使用时应精心设计提示并记录提示内容。</t>
+  </si>
+  <si>
+    <t>明确指出LLMs存在“幻觉”问题，如生成带有偏见、歧视或不实内容的评审意见，举例说明ChatGPT曾因提示生成带有地域偏见的评审文本，强调需人工审核与干预。</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s41073-023-00133-5</t>
+  </si>
+  <si>
+    <t>Hosseini, M., &amp; Horbach, S. P. J. M. (2023). Fighting reviewer fatigue or amplifying bias? Considerations and recommendations for use of ChatGPT and other large language models in scholarly peer review. Research Integrity and Peer Review, 8, 4. https://doi.org/10.1186/s41073-023-00133-5</t>
+  </si>
+  <si>
+    <t>1. 主题框架构建：基于Tennant和Ross-Hellauer的五个同行评审核心主题，构建分析框架；
+2. 案例分析：通过与ChatGPT的交互，展示其在评审任务中的应用（如评估方法描述、生成评审意见、撰写讽刺性评审等）；
+3. 风险识别：指出LLMs在评审中可能带来的偏见、隐私、透明度、可重复性等问题；
+4. 政策建议：提出包括披露使用、接受责任、教育培训、平台监管等在内的多项建议；
+5. 社区呼吁：倡导学术界持续对话与经验共享，推动LLMs在评审中的负责任使用。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BMC Medical Education (2024)</t>
+  </si>
+  <si>
+    <t>LLM‐based automatic short answer grading in undergraduate medical education</t>
+  </si>
+  <si>
+    <t>医学教育中，开放式简答题能更好评估学生知识回忆与理解能力，但人工评分耗时、主观性强。自动短答案评分（ASAG）可缓解此问题。本文首次系统评估GPT-4与Gemini 1.0 Pro在医学本科课程中跨语言（法/英/德）评分的表现，并探讨其一致性、偏差与实用性。</t>
+  </si>
+  <si>
+    <t>ASAG研究始于20世纪60年代，早期依赖规则匹配，后发展为基于统计与机器学习的方法。LLM（如GPT、Gemini）的出现为ASAG带来新机遇，但也引入一致性、偏差、幻觉、隐私等新问题。医学教育领域尚未有LLM-based ASAG的系统研究，本文填补此空白。</t>
+  </si>
+  <si>
+    <t>本文使用GPT-4与Gemini对2288条医学短答案进行自动评分，并与人工评分对比。结果显示：GPT-4评分显著低于人工，但假阳性率低；Gemini评分与人工无显著差异。两模型在完全正确答案上精度高，适合用于“边缘案例”筛选，减轻教师负担。但部分题目存在评分波动，需高质量评分标准与人工监督。</t>
+  </si>
+  <si>
+    <t>研究采用GPT-4与Gemini 1.0 Pro对真实医学考试简答题进行评分，使用统一提示模板，结合评分标准（key）与学生答案，输出0–10分。通过Bland-Altman图、准确率、精度、重评分实验等指标评估模型表现，并分析语言、答案长度对评分的影响。</t>
+  </si>
+  <si>
+    <t>对比GPT-4、Gemini 1.0 Pro与“GPT4b”（已知人工评分）。GPT-4评分偏低但精度高，Gemini评分接近人工，GPT4b因已知人工评分表现出潜在偏差。</t>
+  </si>
+  <si>
+    <t>使用结构化提示，包含系统角色（医学教师）、题目、评分标准、学生答案与满分值。未使用few-shot或链式提示，但指出提示设计对评分结果有显著影响。</t>
+  </si>
+  <si>
+    <t>明确指出LLM存在幻觉风险，可能在解释评分理由时编造内容。建议同时提供评分与解释以避免误导，并强调需人工监督以防 hallucination 影响学生反馈。</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s12909-024-05767-0</t>
+  </si>
+  <si>
+    <t>Grévisse, C. (2024). LLM‐based automatic short answer grading in undergraduate medical education. BMC Medical Education, 24, 1060. https://doi.org/10.1186/s12909-024-05767-0</t>
+  </si>
+  <si>
+    <t>1. 数据收集：从12门医学本科课程中收集2288条学生答案，涵盖法、英、德三种语言；
+2. 模型评分：使用GPT-4、Gemini 1.0 Pro及“GPT4b”（已知人工评分）进行评分，提示包含题目、评分标准、学生答案；
+3. 一致性评估：使用Bland-Altman图、QWK、准确率、精度等指标评估模型与人工评分的一致性；
+4. 重评分实验：对评分差异&gt;0.5的案例进行重评分，分析模型是否调整评分；
+5. 可变性测试：对部分答案重复评分10次，评估模型稳定性；
+6. 语言与长度分析：分析答案语言与长度对评分的影响；
+7. 样本答案评分：评估模型对标准答案的评分表现。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +815,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -203,10 +841,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -232,9 +871,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -513,22 +1159,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="66.125" customWidth="1"/>
-    <col min="5" max="5" width="60.875" customWidth="1"/>
-    <col min="6" max="6" width="59.875" customWidth="1"/>
+    <col min="4" max="4" width="66.08203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="59.83203125" customWidth="1"/>
     <col min="7" max="7" width="65.5" customWidth="1"/>
-    <col min="8" max="8" width="156.125" customWidth="1"/>
+    <col min="8" max="8" width="156.08203125" customWidth="1"/>
     <col min="9" max="9" width="68" customWidth="1"/>
     <col min="10" max="10" width="43.25" style="8" customWidth="1"/>
-    <col min="11" max="12" width="34.875" customWidth="1"/>
+    <col min="11" max="12" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="3" customFormat="1" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -571,7 +1217,7 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="5" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -601,143 +1247,703 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="5" customFormat="1" ht="362.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="309.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:17" s="5" customFormat="1" ht="326.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="403.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:17" s="5" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="365.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:17" s="5" customFormat="1" ht="342" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="297" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" s="5" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="371.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:17" s="5" customFormat="1" ht="365.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="389.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="5" customFormat="1" ht="362.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="309.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="326.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="403.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="365.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="342" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="297" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="371.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="365.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="389.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="406.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="5" customFormat="1" ht="298" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="5" customFormat="1" ht="95.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H19"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H20"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H21"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H22"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H23"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H24"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H25"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H26"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H27"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H28"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H29"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H30"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H31"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H32"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H33"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H34"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H35"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H36"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H37"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H38"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H39"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H40"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H41"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H42"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H43"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="10:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="8:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H44"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="10:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="8:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H45"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="10:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="8:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H46"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="10:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="8:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H47"/>
       <c r="J47" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="L12" r:id="rId1" display="https://aclanthology.org/2024.lrec-main.816/" xr:uid="{D1F8894A-2097-4907-A2C7-A5C6ED5BDB3D}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{16EA4D08-EA91-4256-BB24-5947E3777DED}"/>
+    <hyperlink ref="L11" r:id="rId3" xr:uid="{141E03EB-A25F-4813-9168-F100EE187F5C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>